--- a/故障点位_DB1000.xlsx
+++ b/故障点位_DB1000.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F454"/>
+  <dimension ref="A1:F455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11228,32 +11228,27 @@
       <c r="F380" s="4" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="n">
+      <c r="A381" t="n">
         <v>380</v>
       </c>
-      <c r="B381" s="3" t="inlineStr">
-        <is>
-          <t>预热房通讯</t>
-        </is>
-      </c>
-      <c r="C381" s="4" t="inlineStr">
-        <is>
-          <t>预热房通讯[1]</t>
-        </is>
-      </c>
-      <c r="D381" s="2" t="inlineStr">
-        <is>
-          <t>Bool</t>
-        </is>
-      </c>
-      <c r="E381" s="4" t="inlineStr">
-        <is>
-          <t>DB1000.DBX1984.0</t>
-        </is>
-      </c>
-      <c r="F381" s="4" t="inlineStr">
-        <is>
-          <t>与3201预热通讯中断</t>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>急停</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>控制室急停</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Bool</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>DB1000.DBX1983.0</t>
         </is>
       </c>
     </row>
@@ -11268,7 +11263,7 @@
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>预热房通讯[2]</t>
+          <t>预热房通讯[1]</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
@@ -11278,12 +11273,12 @@
       </c>
       <c r="E382" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1984.1</t>
+          <t>DB1000.DBX1984.0</t>
         </is>
       </c>
       <c r="F382" s="4" t="inlineStr">
         <is>
-          <t>与3202预热通讯中断</t>
+          <t>与3201预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11293,7 @@
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>预热房通讯[3]</t>
+          <t>预热房通讯[2]</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
@@ -11308,12 +11303,12 @@
       </c>
       <c r="E383" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1984.2</t>
+          <t>DB1000.DBX1984.1</t>
         </is>
       </c>
       <c r="F383" s="4" t="inlineStr">
         <is>
-          <t>与3203预热通讯中断</t>
+          <t>与3202预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11323,7 @@
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>预热房通讯[4]</t>
+          <t>预热房通讯[3]</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
@@ -11338,12 +11333,12 @@
       </c>
       <c r="E384" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1984.3</t>
+          <t>DB1000.DBX1984.2</t>
         </is>
       </c>
       <c r="F384" s="4" t="inlineStr">
         <is>
-          <t>与3204预热通讯中断</t>
+          <t>与3203预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11353,7 @@
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>预热房通讯[5]</t>
+          <t>预热房通讯[4]</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
@@ -11368,12 +11363,12 @@
       </c>
       <c r="E385" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1984.4</t>
+          <t>DB1000.DBX1984.3</t>
         </is>
       </c>
       <c r="F385" s="4" t="inlineStr">
         <is>
-          <t>与3205预热通讯中断</t>
+          <t>与3204预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11383,7 @@
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>预热房通讯[6]</t>
+          <t>预热房通讯[5]</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
@@ -11398,12 +11393,12 @@
       </c>
       <c r="E386" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1984.5</t>
+          <t>DB1000.DBX1984.4</t>
         </is>
       </c>
       <c r="F386" s="4" t="inlineStr">
         <is>
-          <t>与3206预热通讯中断</t>
+          <t>与3205预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -11418,7 +11413,7 @@
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>预热房通讯[7]</t>
+          <t>预热房通讯[6]</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
@@ -11428,12 +11423,12 @@
       </c>
       <c r="E387" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1984.6</t>
+          <t>DB1000.DBX1984.5</t>
         </is>
       </c>
       <c r="F387" s="4" t="inlineStr">
         <is>
-          <t>与3207预热通讯中断</t>
+          <t>与3206预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11443,7 @@
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>预热房通讯[8]</t>
+          <t>预热房通讯[7]</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
@@ -11458,12 +11453,12 @@
       </c>
       <c r="E388" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1984.7</t>
+          <t>DB1000.DBX1984.6</t>
         </is>
       </c>
       <c r="F388" s="4" t="inlineStr">
         <is>
-          <t>与3208预热通讯中断</t>
+          <t>与3207预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -11478,7 +11473,7 @@
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>预热房通讯[9]</t>
+          <t>预热房通讯[8]</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
@@ -11488,12 +11483,12 @@
       </c>
       <c r="E389" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1985.0</t>
+          <t>DB1000.DBX1984.7</t>
         </is>
       </c>
       <c r="F389" s="4" t="inlineStr">
         <is>
-          <t>与3209预热通讯中断</t>
+          <t>与3208预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -11508,7 +11503,7 @@
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>预热房通讯[10]</t>
+          <t>预热房通讯[9]</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
@@ -11518,12 +11513,12 @@
       </c>
       <c r="E390" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1985.1</t>
+          <t>DB1000.DBX1985.0</t>
         </is>
       </c>
       <c r="F390" s="4" t="inlineStr">
         <is>
-          <t>与3210预热通讯中断</t>
+          <t>与3209预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -11538,7 +11533,7 @@
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>预热房通讯[11]</t>
+          <t>预热房通讯[10]</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
@@ -11548,12 +11543,12 @@
       </c>
       <c r="E391" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1985.2</t>
+          <t>DB1000.DBX1985.1</t>
         </is>
       </c>
       <c r="F391" s="4" t="inlineStr">
         <is>
-          <t>与3211预热通讯中断</t>
+          <t>与3210预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -11568,7 +11563,7 @@
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>预热房通讯[12]</t>
+          <t>预热房通讯[11]</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
@@ -11578,12 +11573,12 @@
       </c>
       <c r="E392" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1985.3</t>
+          <t>DB1000.DBX1985.2</t>
         </is>
       </c>
       <c r="F392" s="4" t="inlineStr">
         <is>
-          <t>与3212预热通讯中断</t>
+          <t>与3211预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -11598,7 +11593,7 @@
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>预热房通讯[13]</t>
+          <t>预热房通讯[12]</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
@@ -11608,12 +11603,12 @@
       </c>
       <c r="E393" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1985.4</t>
+          <t>DB1000.DBX1985.3</t>
         </is>
       </c>
       <c r="F393" s="4" t="inlineStr">
         <is>
-          <t>与3213预热通讯中断</t>
+          <t>与3212预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11623,7 @@
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>预热房通讯[14]</t>
+          <t>预热房通讯[13]</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
@@ -11638,12 +11633,12 @@
       </c>
       <c r="E394" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1985.5</t>
+          <t>DB1000.DBX1985.4</t>
         </is>
       </c>
       <c r="F394" s="4" t="inlineStr">
         <is>
-          <t>与3214预热通讯中断</t>
+          <t>与3213预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -11658,7 +11653,7 @@
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>预热房通讯[15]</t>
+          <t>预热房通讯[14]</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
@@ -11668,12 +11663,12 @@
       </c>
       <c r="E395" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1985.6</t>
+          <t>DB1000.DBX1985.5</t>
         </is>
       </c>
       <c r="F395" s="4" t="inlineStr">
         <is>
-          <t>与3215预热通讯中断</t>
+          <t>与3214预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -11683,12 +11678,12 @@
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>灭菌柜通讯</t>
+          <t>预热房通讯</t>
         </is>
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>灭菌柜通讯[1]</t>
+          <t>预热房通讯[15]</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
@@ -11698,12 +11693,12 @@
       </c>
       <c r="E396" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1986.0</t>
+          <t>DB1000.DBX1985.6</t>
         </is>
       </c>
       <c r="F396" s="4" t="inlineStr">
         <is>
-          <t>与3201灭菌通讯中断</t>
+          <t>与3215预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11713,7 @@
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>灭菌柜通讯[2]</t>
+          <t>灭菌柜通讯[1]</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
@@ -11728,12 +11723,12 @@
       </c>
       <c r="E397" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1986.1</t>
+          <t>DB1000.DBX1986.0</t>
         </is>
       </c>
       <c r="F397" s="4" t="inlineStr">
         <is>
-          <t>与3202灭菌通讯中断</t>
+          <t>与3201灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11743,7 @@
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>灭菌柜通讯[3]</t>
+          <t>灭菌柜通讯[2]</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
@@ -11758,12 +11753,12 @@
       </c>
       <c r="E398" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1986.2</t>
+          <t>DB1000.DBX1986.1</t>
         </is>
       </c>
       <c r="F398" s="4" t="inlineStr">
         <is>
-          <t>与3203灭菌通讯中断</t>
+          <t>与3202灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11773,7 @@
       </c>
       <c r="C399" s="4" t="inlineStr">
         <is>
-          <t>灭菌柜通讯[4]</t>
+          <t>灭菌柜通讯[3]</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
@@ -11788,12 +11783,12 @@
       </c>
       <c r="E399" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1986.3</t>
+          <t>DB1000.DBX1986.2</t>
         </is>
       </c>
       <c r="F399" s="4" t="inlineStr">
         <is>
-          <t>与3204灭菌通讯中断</t>
+          <t>与3203灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -11808,7 +11803,7 @@
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>灭菌柜通讯[5]</t>
+          <t>灭菌柜通讯[4]</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
@@ -11818,12 +11813,12 @@
       </c>
       <c r="E400" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1986.4</t>
+          <t>DB1000.DBX1986.3</t>
         </is>
       </c>
       <c r="F400" s="4" t="inlineStr">
         <is>
-          <t>与3205灭菌通讯中断</t>
+          <t>与3204灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -11838,7 +11833,7 @@
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>灭菌柜通讯[6]</t>
+          <t>灭菌柜通讯[5]</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
@@ -11848,12 +11843,12 @@
       </c>
       <c r="E401" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1986.5</t>
+          <t>DB1000.DBX1986.4</t>
         </is>
       </c>
       <c r="F401" s="4" t="inlineStr">
         <is>
-          <t>与3206灭菌通讯中断</t>
+          <t>与3205灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -11868,7 +11863,7 @@
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>灭菌柜通讯[7]</t>
+          <t>灭菌柜通讯[6]</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
@@ -11878,12 +11873,12 @@
       </c>
       <c r="E402" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1986.6</t>
+          <t>DB1000.DBX1986.5</t>
         </is>
       </c>
       <c r="F402" s="4" t="inlineStr">
         <is>
-          <t>与3207灭菌通讯中断</t>
+          <t>与3206灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -11898,7 +11893,7 @@
       </c>
       <c r="C403" s="4" t="inlineStr">
         <is>
-          <t>灭菌柜通讯[8]</t>
+          <t>灭菌柜通讯[7]</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
@@ -11908,12 +11903,12 @@
       </c>
       <c r="E403" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1986.7</t>
+          <t>DB1000.DBX1986.6</t>
         </is>
       </c>
       <c r="F403" s="4" t="inlineStr">
         <is>
-          <t>与3208灭菌通讯中断</t>
+          <t>与3207灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11923,7 @@
       </c>
       <c r="C404" s="4" t="inlineStr">
         <is>
-          <t>灭菌柜通讯[9]</t>
+          <t>灭菌柜通讯[8]</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
@@ -11938,12 +11933,12 @@
       </c>
       <c r="E404" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1987.0</t>
+          <t>DB1000.DBX1986.7</t>
         </is>
       </c>
       <c r="F404" s="4" t="inlineStr">
         <is>
-          <t>与3209灭菌通讯中断</t>
+          <t>与3208灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -11958,7 +11953,7 @@
       </c>
       <c r="C405" s="4" t="inlineStr">
         <is>
-          <t>灭菌柜通讯[10]</t>
+          <t>灭菌柜通讯[9]</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
@@ -11968,12 +11963,12 @@
       </c>
       <c r="E405" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1987.1</t>
+          <t>DB1000.DBX1987.0</t>
         </is>
       </c>
       <c r="F405" s="4" t="inlineStr">
         <is>
-          <t>与3210灭菌通讯中断</t>
+          <t>与3209灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -11988,7 +11983,7 @@
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>灭菌柜通讯[11]</t>
+          <t>灭菌柜通讯[10]</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
@@ -11998,12 +11993,12 @@
       </c>
       <c r="E406" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1987.2</t>
+          <t>DB1000.DBX1987.1</t>
         </is>
       </c>
       <c r="F406" s="4" t="inlineStr">
         <is>
-          <t>与3211灭菌通讯中断</t>
+          <t>与3210灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12013,7 @@
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>灭菌柜通讯[12]</t>
+          <t>灭菌柜通讯[11]</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
@@ -12028,12 +12023,12 @@
       </c>
       <c r="E407" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1987.3</t>
+          <t>DB1000.DBX1987.2</t>
         </is>
       </c>
       <c r="F407" s="4" t="inlineStr">
         <is>
-          <t>与3212灭菌通讯中断</t>
+          <t>与3211灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12048,7 +12043,7 @@
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>灭菌柜通讯[13]</t>
+          <t>灭菌柜通讯[12]</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
@@ -12058,12 +12053,12 @@
       </c>
       <c r="E408" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1987.4</t>
+          <t>DB1000.DBX1987.3</t>
         </is>
       </c>
       <c r="F408" s="4" t="inlineStr">
         <is>
-          <t>与3213灭菌通讯中断</t>
+          <t>与3212灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12078,7 +12073,7 @@
       </c>
       <c r="C409" s="4" t="inlineStr">
         <is>
-          <t>灭菌柜通讯[14]</t>
+          <t>灭菌柜通讯[13]</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
@@ -12088,12 +12083,12 @@
       </c>
       <c r="E409" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1987.5</t>
+          <t>DB1000.DBX1987.4</t>
         </is>
       </c>
       <c r="F409" s="4" t="inlineStr">
         <is>
-          <t>与3214灭菌通讯中断</t>
+          <t>与3213灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12108,7 +12103,7 @@
       </c>
       <c r="C410" s="4" t="inlineStr">
         <is>
-          <t>灭菌柜通讯[15]</t>
+          <t>灭菌柜通讯[14]</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
@@ -12118,12 +12113,12 @@
       </c>
       <c r="E410" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1987.6</t>
+          <t>DB1000.DBX1987.5</t>
         </is>
       </c>
       <c r="F410" s="4" t="inlineStr">
         <is>
-          <t>与3215灭菌通讯中断</t>
+          <t>与3214灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12131,14 +12126,14 @@
       <c r="A411" s="2" t="n">
         <v>410</v>
       </c>
-      <c r="B411" s="9" t="inlineStr">
-        <is>
-          <t>预热信号箱</t>
+      <c r="B411" s="3" t="inlineStr">
+        <is>
+          <t>灭菌柜通讯</t>
         </is>
       </c>
       <c r="C411" s="4" t="inlineStr">
         <is>
-          <t>预热信号箱[1]</t>
+          <t>灭菌柜通讯[15]</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
@@ -12148,12 +12143,12 @@
       </c>
       <c r="E411" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1988.0</t>
+          <t>DB1000.DBX1987.6</t>
         </is>
       </c>
       <c r="F411" s="4" t="inlineStr">
         <is>
-          <t>与3201预热通讯中断</t>
+          <t>与3215灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12163,7 @@
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>预热信号箱[2]</t>
+          <t>预热信号箱[1]</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
@@ -12178,12 +12173,12 @@
       </c>
       <c r="E412" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1988.1</t>
+          <t>DB1000.DBX1988.0</t>
         </is>
       </c>
       <c r="F412" s="4" t="inlineStr">
         <is>
-          <t>与3202预热通讯中断</t>
+          <t>与3201预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12193,7 @@
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>预热信号箱[3]</t>
+          <t>预热信号箱[2]</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
@@ -12208,12 +12203,12 @@
       </c>
       <c r="E413" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1988.2</t>
+          <t>DB1000.DBX1988.1</t>
         </is>
       </c>
       <c r="F413" s="4" t="inlineStr">
         <is>
-          <t>与3203预热通讯中断</t>
+          <t>与3202预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -12228,7 +12223,7 @@
       </c>
       <c r="C414" s="4" t="inlineStr">
         <is>
-          <t>预热信号箱[4]</t>
+          <t>预热信号箱[3]</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
@@ -12238,12 +12233,12 @@
       </c>
       <c r="E414" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1988.3</t>
+          <t>DB1000.DBX1988.2</t>
         </is>
       </c>
       <c r="F414" s="4" t="inlineStr">
         <is>
-          <t>与3204预热通讯中断</t>
+          <t>与3203预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12253,7 @@
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>预热信号箱[5]</t>
+          <t>预热信号箱[4]</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
@@ -12268,12 +12263,12 @@
       </c>
       <c r="E415" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1988.4</t>
+          <t>DB1000.DBX1988.3</t>
         </is>
       </c>
       <c r="F415" s="4" t="inlineStr">
         <is>
-          <t>与3205预热通讯中断</t>
+          <t>与3204预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -12288,7 +12283,7 @@
       </c>
       <c r="C416" s="4" t="inlineStr">
         <is>
-          <t>预热信号箱[6]</t>
+          <t>预热信号箱[5]</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
@@ -12298,12 +12293,12 @@
       </c>
       <c r="E416" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1988.5</t>
+          <t>DB1000.DBX1988.4</t>
         </is>
       </c>
       <c r="F416" s="4" t="inlineStr">
         <is>
-          <t>与3206预热通讯中断</t>
+          <t>与3205预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -12318,7 +12313,7 @@
       </c>
       <c r="C417" s="4" t="inlineStr">
         <is>
-          <t>预热信号箱[7]</t>
+          <t>预热信号箱[6]</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
@@ -12328,12 +12323,12 @@
       </c>
       <c r="E417" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1988.6</t>
+          <t>DB1000.DBX1988.5</t>
         </is>
       </c>
       <c r="F417" s="4" t="inlineStr">
         <is>
-          <t>与3207预热通讯中断</t>
+          <t>与3206预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -12348,7 +12343,7 @@
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>预热信号箱[8]</t>
+          <t>预热信号箱[7]</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
@@ -12358,12 +12353,12 @@
       </c>
       <c r="E418" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1988.7</t>
+          <t>DB1000.DBX1988.6</t>
         </is>
       </c>
       <c r="F418" s="4" t="inlineStr">
         <is>
-          <t>与3208预热通讯中断</t>
+          <t>与3207预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -12378,7 +12373,7 @@
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>预热信号箱[9]</t>
+          <t>预热信号箱[8]</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
@@ -12388,12 +12383,12 @@
       </c>
       <c r="E419" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1989.0</t>
+          <t>DB1000.DBX1988.7</t>
         </is>
       </c>
       <c r="F419" s="4" t="inlineStr">
         <is>
-          <t>与3209预热通讯中断</t>
+          <t>与3208预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -12408,7 +12403,7 @@
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>预热信号箱[10]</t>
+          <t>预热信号箱[9]</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
@@ -12418,12 +12413,12 @@
       </c>
       <c r="E420" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1989.1</t>
+          <t>DB1000.DBX1989.0</t>
         </is>
       </c>
       <c r="F420" s="4" t="inlineStr">
         <is>
-          <t>与3210预热通讯中断</t>
+          <t>与3209预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -12438,7 +12433,7 @@
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>预热信号箱[11]</t>
+          <t>预热信号箱[10]</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
@@ -12448,12 +12443,12 @@
       </c>
       <c r="E421" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1989.2</t>
+          <t>DB1000.DBX1989.1</t>
         </is>
       </c>
       <c r="F421" s="4" t="inlineStr">
         <is>
-          <t>与3211预热通讯中断</t>
+          <t>与3210预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12463,7 @@
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>预热信号箱[12]</t>
+          <t>预热信号箱[11]</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
@@ -12478,12 +12473,12 @@
       </c>
       <c r="E422" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1989.3</t>
+          <t>DB1000.DBX1989.2</t>
         </is>
       </c>
       <c r="F422" s="4" t="inlineStr">
         <is>
-          <t>与3212预热通讯中断</t>
+          <t>与3211预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -12498,7 +12493,7 @@
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>预热信号箱[13]</t>
+          <t>预热信号箱[12]</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
@@ -12508,12 +12503,12 @@
       </c>
       <c r="E423" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1989.4</t>
+          <t>DB1000.DBX1989.3</t>
         </is>
       </c>
       <c r="F423" s="4" t="inlineStr">
         <is>
-          <t>与3213预热通讯中断</t>
+          <t>与3212预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -12528,7 +12523,7 @@
       </c>
       <c r="C424" s="4" t="inlineStr">
         <is>
-          <t>预热信号箱[14]</t>
+          <t>预热信号箱[13]</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
@@ -12538,12 +12533,12 @@
       </c>
       <c r="E424" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1989.5</t>
+          <t>DB1000.DBX1989.4</t>
         </is>
       </c>
       <c r="F424" s="4" t="inlineStr">
         <is>
-          <t>与3214预热通讯中断</t>
+          <t>与3213预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -12558,7 +12553,7 @@
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>预热信号箱[15]</t>
+          <t>预热信号箱[14]</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
@@ -12568,12 +12563,12 @@
       </c>
       <c r="E425" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1989.6</t>
+          <t>DB1000.DBX1989.5</t>
         </is>
       </c>
       <c r="F425" s="4" t="inlineStr">
         <is>
-          <t>与3215预热通讯中断</t>
+          <t>与3214预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -12583,12 +12578,12 @@
       </c>
       <c r="B426" s="9" t="inlineStr">
         <is>
-          <t>灭菌信号箱</t>
+          <t>预热信号箱</t>
         </is>
       </c>
       <c r="C426" s="4" t="inlineStr">
         <is>
-          <t>灭菌信号箱[1]</t>
+          <t>预热信号箱[15]</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
@@ -12598,12 +12593,12 @@
       </c>
       <c r="E426" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1990.0</t>
+          <t>DB1000.DBX1989.6</t>
         </is>
       </c>
       <c r="F426" s="4" t="inlineStr">
         <is>
-          <t>与3201灭菌通讯中断</t>
+          <t>与3215预热通讯中断</t>
         </is>
       </c>
     </row>
@@ -12618,7 +12613,7 @@
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>灭菌信号箱[2]</t>
+          <t>灭菌信号箱[1]</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
@@ -12628,12 +12623,12 @@
       </c>
       <c r="E427" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1990.1</t>
+          <t>DB1000.DBX1990.0</t>
         </is>
       </c>
       <c r="F427" s="4" t="inlineStr">
         <is>
-          <t>与3202灭菌通讯中断</t>
+          <t>与3201灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12643,7 @@
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>灭菌信号箱[3]</t>
+          <t>灭菌信号箱[2]</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
@@ -12658,12 +12653,12 @@
       </c>
       <c r="E428" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1990.2</t>
+          <t>DB1000.DBX1990.1</t>
         </is>
       </c>
       <c r="F428" s="4" t="inlineStr">
         <is>
-          <t>与3203灭菌通讯中断</t>
+          <t>与3202灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12678,7 +12673,7 @@
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>灭菌信号箱[4]</t>
+          <t>灭菌信号箱[3]</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
@@ -12688,12 +12683,12 @@
       </c>
       <c r="E429" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1990.3</t>
+          <t>DB1000.DBX1990.2</t>
         </is>
       </c>
       <c r="F429" s="4" t="inlineStr">
         <is>
-          <t>与3204灭菌通讯中断</t>
+          <t>与3203灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12703,7 @@
       </c>
       <c r="C430" s="4" t="inlineStr">
         <is>
-          <t>灭菌信号箱[5]</t>
+          <t>灭菌信号箱[4]</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
@@ -12718,12 +12713,12 @@
       </c>
       <c r="E430" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1990.4</t>
+          <t>DB1000.DBX1990.3</t>
         </is>
       </c>
       <c r="F430" s="4" t="inlineStr">
         <is>
-          <t>与3205灭菌通讯中断</t>
+          <t>与3204灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12738,7 +12733,7 @@
       </c>
       <c r="C431" s="4" t="inlineStr">
         <is>
-          <t>灭菌信号箱[6]</t>
+          <t>灭菌信号箱[5]</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
@@ -12748,12 +12743,12 @@
       </c>
       <c r="E431" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1990.5</t>
+          <t>DB1000.DBX1990.4</t>
         </is>
       </c>
       <c r="F431" s="4" t="inlineStr">
         <is>
-          <t>与3206灭菌通讯中断</t>
+          <t>与3205灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12763,7 @@
       </c>
       <c r="C432" s="4" t="inlineStr">
         <is>
-          <t>灭菌信号箱[7]</t>
+          <t>灭菌信号箱[6]</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
@@ -12778,12 +12773,12 @@
       </c>
       <c r="E432" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1990.6</t>
+          <t>DB1000.DBX1990.5</t>
         </is>
       </c>
       <c r="F432" s="4" t="inlineStr">
         <is>
-          <t>与3207灭菌通讯中断</t>
+          <t>与3206灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12793,7 @@
       </c>
       <c r="C433" s="4" t="inlineStr">
         <is>
-          <t>灭菌信号箱[8]</t>
+          <t>灭菌信号箱[7]</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
@@ -12808,12 +12803,12 @@
       </c>
       <c r="E433" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1990.7</t>
+          <t>DB1000.DBX1990.6</t>
         </is>
       </c>
       <c r="F433" s="4" t="inlineStr">
         <is>
-          <t>与3208灭菌通讯中断</t>
+          <t>与3207灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12828,7 +12823,7 @@
       </c>
       <c r="C434" s="4" t="inlineStr">
         <is>
-          <t>灭菌信号箱[9]</t>
+          <t>灭菌信号箱[8]</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
@@ -12838,12 +12833,12 @@
       </c>
       <c r="E434" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1991.0</t>
+          <t>DB1000.DBX1990.7</t>
         </is>
       </c>
       <c r="F434" s="4" t="inlineStr">
         <is>
-          <t>与3209灭菌通讯中断</t>
+          <t>与3208灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12858,7 +12853,7 @@
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>灭菌信号箱[10]</t>
+          <t>灭菌信号箱[9]</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
@@ -12868,12 +12863,12 @@
       </c>
       <c r="E435" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1991.1</t>
+          <t>DB1000.DBX1991.0</t>
         </is>
       </c>
       <c r="F435" s="4" t="inlineStr">
         <is>
-          <t>与3210灭菌通讯中断</t>
+          <t>与3209灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12888,7 +12883,7 @@
       </c>
       <c r="C436" s="4" t="inlineStr">
         <is>
-          <t>灭菌信号箱[11]</t>
+          <t>灭菌信号箱[10]</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
@@ -12898,12 +12893,12 @@
       </c>
       <c r="E436" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1991.2</t>
+          <t>DB1000.DBX1991.1</t>
         </is>
       </c>
       <c r="F436" s="4" t="inlineStr">
         <is>
-          <t>与3211灭菌通讯中断</t>
+          <t>与3210灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12918,7 +12913,7 @@
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>灭菌信号箱[12]</t>
+          <t>灭菌信号箱[11]</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
@@ -12928,12 +12923,12 @@
       </c>
       <c r="E437" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1991.3</t>
+          <t>DB1000.DBX1991.2</t>
         </is>
       </c>
       <c r="F437" s="4" t="inlineStr">
         <is>
-          <t>与3212灭菌通讯中断</t>
+          <t>与3211灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12943,7 @@
       </c>
       <c r="C438" s="4" t="inlineStr">
         <is>
-          <t>灭菌信号箱[13]</t>
+          <t>灭菌信号箱[12]</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
@@ -12958,12 +12953,12 @@
       </c>
       <c r="E438" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1991.4</t>
+          <t>DB1000.DBX1991.3</t>
         </is>
       </c>
       <c r="F438" s="4" t="inlineStr">
         <is>
-          <t>与3213灭菌通讯中断</t>
+          <t>与3212灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -12978,7 +12973,7 @@
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>灭菌信号箱[14]</t>
+          <t>灭菌信号箱[13]</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
@@ -12988,12 +12983,12 @@
       </c>
       <c r="E439" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1991.5</t>
+          <t>DB1000.DBX1991.4</t>
         </is>
       </c>
       <c r="F439" s="4" t="inlineStr">
         <is>
-          <t>与3214灭菌通讯中断</t>
+          <t>与3213灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -13008,7 +13003,7 @@
       </c>
       <c r="C440" s="4" t="inlineStr">
         <is>
-          <t>灭菌信号箱[15]</t>
+          <t>灭菌信号箱[14]</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
@@ -13018,12 +13013,12 @@
       </c>
       <c r="E440" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1991.6</t>
+          <t>DB1000.DBX1991.5</t>
         </is>
       </c>
       <c r="F440" s="4" t="inlineStr">
         <is>
-          <t>与3215灭菌通讯中断</t>
+          <t>与3214灭菌通讯中断</t>
         </is>
       </c>
     </row>
@@ -13033,12 +13028,12 @@
       </c>
       <c r="B441" s="9" t="inlineStr">
         <is>
-          <t>信号箱</t>
+          <t>灭菌信号箱</t>
         </is>
       </c>
       <c r="C441" s="4" t="inlineStr">
         <is>
-          <t>上线信号箱</t>
+          <t>灭菌信号箱[15]</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
@@ -13048,10 +13043,14 @@
       </c>
       <c r="E441" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1992.0</t>
-        </is>
-      </c>
-      <c r="F441" s="4" t="inlineStr"/>
+          <t>DB1000.DBX1991.6</t>
+        </is>
+      </c>
+      <c r="F441" s="4" t="inlineStr">
+        <is>
+          <t>与3215灭菌通讯中断</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
@@ -13064,7 +13063,7 @@
       </c>
       <c r="C442" s="4" t="inlineStr">
         <is>
-          <t>下线信号箱</t>
+          <t>上线信号箱</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
@@ -13074,7 +13073,7 @@
       </c>
       <c r="E442" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1992.1</t>
+          <t>DB1000.DBX1992.0</t>
         </is>
       </c>
       <c r="F442" s="4" t="inlineStr"/>
@@ -13090,7 +13089,7 @@
       </c>
       <c r="C443" s="4" t="inlineStr">
         <is>
-          <t>RGV信号箱</t>
+          <t>下线信号箱</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
@@ -13100,7 +13099,7 @@
       </c>
       <c r="E443" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1992.2</t>
+          <t>DB1000.DBX1992.1</t>
         </is>
       </c>
       <c r="F443" s="4" t="inlineStr"/>
@@ -13109,14 +13108,14 @@
       <c r="A444" s="2" t="n">
         <v>443</v>
       </c>
-      <c r="B444" s="6" t="inlineStr">
-        <is>
-          <t>上线气缸</t>
+      <c r="B444" s="9" t="inlineStr">
+        <is>
+          <t>信号箱</t>
         </is>
       </c>
       <c r="C444" s="4" t="inlineStr">
         <is>
-          <t>上线气缸[0]</t>
+          <t>RGV信号箱</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
@@ -13126,14 +13125,10 @@
       </c>
       <c r="E444" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1994.0</t>
-        </is>
-      </c>
-      <c r="F444" s="4" t="inlineStr">
-        <is>
-          <t>上线01002左侧托盘剧中气缸超时</t>
-        </is>
-      </c>
+          <t>DB1000.DBX1992.2</t>
+        </is>
+      </c>
+      <c r="F444" s="4" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
@@ -13146,7 +13141,7 @@
       </c>
       <c r="C445" s="4" t="inlineStr">
         <is>
-          <t>上线气缸[1]</t>
+          <t>上线气缸[0]</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
@@ -13156,12 +13151,12 @@
       </c>
       <c r="E445" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1994.1</t>
+          <t>DB1000.DBX1994.0</t>
         </is>
       </c>
       <c r="F445" s="4" t="inlineStr">
         <is>
-          <t>上线01002右侧托盘剧中气缸超时</t>
+          <t>上线01002左侧托盘剧中气缸超时</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13171,7 @@
       </c>
       <c r="C446" s="4" t="inlineStr">
         <is>
-          <t>上线气缸[2]</t>
+          <t>上线气缸[1]</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
@@ -13186,12 +13181,12 @@
       </c>
       <c r="E446" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1994.2</t>
+          <t>DB1000.DBX1994.1</t>
         </is>
       </c>
       <c r="F446" s="4" t="inlineStr">
         <is>
-          <t>上线01002左侧货物剧中气缸超时</t>
+          <t>上线01002右侧托盘剧中气缸超时</t>
         </is>
       </c>
     </row>
@@ -13206,7 +13201,7 @@
       </c>
       <c r="C447" s="4" t="inlineStr">
         <is>
-          <t>上线气缸[3]</t>
+          <t>上线气缸[2]</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
@@ -13216,12 +13211,12 @@
       </c>
       <c r="E447" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1994.3</t>
+          <t>DB1000.DBX1994.2</t>
         </is>
       </c>
       <c r="F447" s="4" t="inlineStr">
         <is>
-          <t>上线01002右侧货物剧中气缸超时</t>
+          <t>上线01002左侧货物剧中气缸超时</t>
         </is>
       </c>
     </row>
@@ -13236,7 +13231,7 @@
       </c>
       <c r="C448" s="4" t="inlineStr">
         <is>
-          <t>上线气缸[4]</t>
+          <t>上线气缸[3]</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
@@ -13246,12 +13241,12 @@
       </c>
       <c r="E448" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1994.4</t>
+          <t>DB1000.DBX1994.3</t>
         </is>
       </c>
       <c r="F448" s="4" t="inlineStr">
         <is>
-          <t>上线01006左侧货物剧中气缸超时</t>
+          <t>上线01002右侧货物剧中气缸超时</t>
         </is>
       </c>
     </row>
@@ -13266,7 +13261,7 @@
       </c>
       <c r="C449" s="4" t="inlineStr">
         <is>
-          <t>上线气缸[5]</t>
+          <t>上线气缸[4]</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
@@ -13276,12 +13271,12 @@
       </c>
       <c r="E449" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1994.5</t>
+          <t>DB1000.DBX1994.4</t>
         </is>
       </c>
       <c r="F449" s="4" t="inlineStr">
         <is>
-          <t>上线01006右侧货物剧中气缸超时</t>
+          <t>上线01006左侧货物剧中气缸超时</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13291,7 @@
       </c>
       <c r="C450" s="4" t="inlineStr">
         <is>
-          <t>上线气缸[6]</t>
+          <t>上线气缸[5]</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
@@ -13306,10 +13301,14 @@
       </c>
       <c r="E450" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1994.6</t>
-        </is>
-      </c>
-      <c r="F450" s="4" t="inlineStr"/>
+          <t>DB1000.DBX1994.5</t>
+        </is>
+      </c>
+      <c r="F450" s="4" t="inlineStr">
+        <is>
+          <t>上线01006右侧货物剧中气缸超时</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
@@ -13322,7 +13321,7 @@
       </c>
       <c r="C451" s="4" t="inlineStr">
         <is>
-          <t>上线气缸[7]</t>
+          <t>上线气缸[6]</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
@@ -13332,7 +13331,7 @@
       </c>
       <c r="E451" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1994.7</t>
+          <t>DB1000.DBX1994.6</t>
         </is>
       </c>
       <c r="F451" s="4" t="inlineStr"/>
@@ -13348,7 +13347,7 @@
       </c>
       <c r="C452" s="4" t="inlineStr">
         <is>
-          <t>上线气缸[8]</t>
+          <t>上线气缸[7]</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
@@ -13358,7 +13357,7 @@
       </c>
       <c r="E452" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1995.0</t>
+          <t>DB1000.DBX1994.7</t>
         </is>
       </c>
       <c r="F452" s="4" t="inlineStr"/>
@@ -13374,7 +13373,7 @@
       </c>
       <c r="C453" s="4" t="inlineStr">
         <is>
-          <t>上线气缸[9]</t>
+          <t>上线气缸[8]</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
@@ -13384,7 +13383,7 @@
       </c>
       <c r="E453" s="4" t="inlineStr">
         <is>
-          <t>DB1000.DBX1995.1</t>
+          <t>DB1000.DBX1995.0</t>
         </is>
       </c>
       <c r="F453" s="4" t="inlineStr"/>
@@ -13400,20 +13399,46 @@
       </c>
       <c r="C454" s="4" t="inlineStr">
         <is>
+          <t>上线气缸[9]</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>Bool</t>
+        </is>
+      </c>
+      <c r="E454" s="4" t="inlineStr">
+        <is>
+          <t>DB1000.DBX1995.1</t>
+        </is>
+      </c>
+      <c r="F454" s="4" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="n">
+        <v>454</v>
+      </c>
+      <c r="B455" s="6" t="inlineStr">
+        <is>
+          <t>上线气缸</t>
+        </is>
+      </c>
+      <c r="C455" s="4" t="inlineStr">
+        <is>
           <t>上线气缸[10]</t>
         </is>
       </c>
-      <c r="D454" s="2" t="inlineStr">
-        <is>
-          <t>Bool</t>
-        </is>
-      </c>
-      <c r="E454" s="4" t="inlineStr">
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>Bool</t>
+        </is>
+      </c>
+      <c r="E455" s="4" t="inlineStr">
         <is>
           <t>DB1000.DBX1995.2</t>
         </is>
       </c>
-      <c r="F454" s="4" t="inlineStr"/>
+      <c r="F455" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F454"/>
